--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/group_roi_means_wmprob.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/group_roi_means_wmprob.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -271,40 +272,40 @@
         <v>23</v>
       </c>
       <c r="D2" s="0">
-        <v>0.54320698976516724</v>
+        <v>0.4152987003326416</v>
       </c>
       <c r="E2" s="0">
-        <v>0.49742192029953003</v>
+        <v>0.37360090017318726</v>
       </c>
       <c r="F2" s="0">
-        <v>0.51605027914047241</v>
+        <v>0.40151494741439819</v>
       </c>
       <c r="G2" s="0">
-        <v>0.48967477679252625</v>
+        <v>0.37267488241195679</v>
       </c>
       <c r="H2" s="0">
-        <v>0.52370262145996094</v>
+        <v>0.42089039087295532</v>
       </c>
       <c r="I2" s="0">
-        <v>0.52856099605560303</v>
+        <v>0.42297074198722839</v>
       </c>
       <c r="J2" s="0">
-        <v>0.51277023553848267</v>
+        <v>0.40680575370788574</v>
       </c>
       <c r="K2" s="0">
-        <v>0.5271759033203125</v>
+        <v>0.42024514079093933</v>
       </c>
       <c r="L2" s="0">
-        <v>0.51875317096710205</v>
+        <v>0.38919037580490112</v>
       </c>
       <c r="M2" s="0">
-        <v>0.52673274278640747</v>
+        <v>0.41962498426437378</v>
       </c>
       <c r="N2" s="0">
-        <v>0.48252618312835693</v>
+        <v>0.37113434076309204</v>
       </c>
       <c r="O2" s="0">
-        <v>0.53151082992553711</v>
+        <v>0.42784786224365234</v>
       </c>
     </row>
     <row r="3">
@@ -318,40 +319,40 @@
         <v>24</v>
       </c>
       <c r="D3" s="0">
-        <v>0.40857771039009094</v>
+        <v>0.49108612537384033</v>
       </c>
       <c r="E3" s="0">
-        <v>0.3826490044593811</v>
+        <v>0.47122898697853088</v>
       </c>
       <c r="F3" s="0">
-        <v>0.39568129181861877</v>
+        <v>0.47834470868110657</v>
       </c>
       <c r="G3" s="0">
-        <v>0.37220469117164612</v>
+        <v>0.46996113657951355</v>
       </c>
       <c r="H3" s="0">
-        <v>0.43329045176506042</v>
+        <v>0.48502779006958008</v>
       </c>
       <c r="I3" s="0">
-        <v>0.41717582941055298</v>
+        <v>0.47937360405921936</v>
       </c>
       <c r="J3" s="0">
-        <v>0.418781578540802</v>
+        <v>0.46989989280700684</v>
       </c>
       <c r="K3" s="0">
-        <v>0.41187059879302979</v>
+        <v>0.49651026725769043</v>
       </c>
       <c r="L3" s="0">
-        <v>0.37885922193527222</v>
+        <v>0.47332847118377686</v>
       </c>
       <c r="M3" s="0">
-        <v>0.40489888191223145</v>
+        <v>0.47948095202445984</v>
       </c>
       <c r="N3" s="0">
-        <v>0.35588943958282471</v>
+        <v>0.43116763234138489</v>
       </c>
       <c r="O3" s="0">
-        <v>0.41143885254859924</v>
+        <v>0.49241554737091065</v>
       </c>
     </row>
     <row r="4">
@@ -365,40 +366,40 @@
         <v>25</v>
       </c>
       <c r="D4" s="0">
-        <v>0.47712716460227966</v>
+        <v>0.61485660076141358</v>
       </c>
       <c r="E4" s="0">
-        <v>0.453969806432724</v>
+        <v>0.6008567214012146</v>
       </c>
       <c r="F4" s="0">
-        <v>0.45571735501289368</v>
+        <v>0.62222576141357422</v>
       </c>
       <c r="G4" s="0">
-        <v>0.4635729193687439</v>
+        <v>0.58690565824508667</v>
       </c>
       <c r="H4" s="0">
-        <v>0.48745310306549072</v>
+        <v>0.63243180513381958</v>
       </c>
       <c r="I4" s="0">
-        <v>0.46568518877029419</v>
+        <v>0.62749427556991577</v>
       </c>
       <c r="J4" s="0">
-        <v>0.47154620289802551</v>
+        <v>0.64002645015716553</v>
       </c>
       <c r="K4" s="0">
-        <v>0.48424839973449707</v>
+        <v>0.62652981281280518</v>
       </c>
       <c r="L4" s="0">
-        <v>0.46134239435195923</v>
+        <v>0.62028002738952637</v>
       </c>
       <c r="M4" s="0">
-        <v>0.46625009179115295</v>
+        <v>0.62140661478042603</v>
       </c>
       <c r="N4" s="0">
-        <v>0.42565497756004333</v>
+        <v>0.56462383270263672</v>
       </c>
       <c r="O4" s="0">
-        <v>0.47428634762763977</v>
+        <v>0.6115984320640564</v>
       </c>
     </row>
     <row r="5">
@@ -412,40 +413,40 @@
         <v>26</v>
       </c>
       <c r="D5" s="0">
-        <v>0.41216984391212463</v>
+        <v>0.61197537183761597</v>
       </c>
       <c r="E5" s="0">
-        <v>0.39627513289451599</v>
+        <v>0.57107251882553101</v>
       </c>
       <c r="F5" s="0">
-        <v>0.40895158052444458</v>
+        <v>0.59443247318267822</v>
       </c>
       <c r="G5" s="0">
-        <v>0.38054138422012329</v>
+        <v>0.56170237064361572</v>
       </c>
       <c r="H5" s="0">
-        <v>0.39519196748733521</v>
+        <v>0.59712916612625122</v>
       </c>
       <c r="I5" s="0">
-        <v>0.41689026355743408</v>
+        <v>0.60706239938735962</v>
       </c>
       <c r="J5" s="0">
-        <v>0.4145929217338562</v>
+        <v>0.60258811712265015</v>
       </c>
       <c r="K5" s="0">
-        <v>0.42393088340759277</v>
+        <v>0.60937720537185669</v>
       </c>
       <c r="L5" s="0">
-        <v>0.40463897585868835</v>
+        <v>0.58911395072937012</v>
       </c>
       <c r="M5" s="0">
-        <v>0.41835656762123108</v>
+        <v>0.6055753231048584</v>
       </c>
       <c r="N5" s="0">
-        <v>0.35989272594451904</v>
+        <v>0.5459480881690979</v>
       </c>
       <c r="O5" s="0">
-        <v>0.41386893391609192</v>
+        <v>0.60651707649230957</v>
       </c>
     </row>
     <row r="6">
@@ -459,40 +460,40 @@
         <v>27</v>
       </c>
       <c r="D6" s="0">
-        <v>0.53906679153442383</v>
+        <v>0.5758056640625</v>
       </c>
       <c r="E6" s="0">
-        <v>0.53158140182495117</v>
+        <v>0.53248381614685059</v>
       </c>
       <c r="F6" s="0">
-        <v>0.52161413431167603</v>
+        <v>0.56393855810165405</v>
       </c>
       <c r="G6" s="0">
-        <v>0.50661790370941162</v>
+        <v>0.53287589550018311</v>
       </c>
       <c r="H6" s="0">
-        <v>0.54588675498962402</v>
+        <v>0.55216401815414429</v>
       </c>
       <c r="I6" s="0">
-        <v>0.52719801664352417</v>
+        <v>0.56525516510009766</v>
       </c>
       <c r="J6" s="0">
-        <v>0.53834289312362671</v>
+        <v>0.55154585838317871</v>
       </c>
       <c r="K6" s="0">
-        <v>0.53222459554672241</v>
+        <v>0.5760345458984375</v>
       </c>
       <c r="L6" s="0">
-        <v>0.51174664497375488</v>
+        <v>0.53858655691146851</v>
       </c>
       <c r="M6" s="0">
-        <v>0.53996485471725464</v>
+        <v>0.5900081992149353</v>
       </c>
       <c r="N6" s="0">
-        <v>0.48211079835891724</v>
+        <v>0.53053158521652222</v>
       </c>
       <c r="O6" s="0">
-        <v>0.53866231441497803</v>
+        <v>0.55689436197280884</v>
       </c>
     </row>
     <row r="7">
@@ -506,40 +507,40 @@
         <v>28</v>
       </c>
       <c r="D7" s="0">
-        <v>0.50485795736312866</v>
+        <v>0.61855727434158325</v>
       </c>
       <c r="E7" s="0">
-        <v>0.45140445232391357</v>
+        <v>0.57314908504486084</v>
       </c>
       <c r="F7" s="0">
-        <v>0.46935120224952698</v>
+        <v>0.58069467544555664</v>
       </c>
       <c r="G7" s="0">
-        <v>0.44673016667366028</v>
+        <v>0.54474180936813355</v>
       </c>
       <c r="H7" s="0">
-        <v>0.49311602115631104</v>
+        <v>0.59481126070022583</v>
       </c>
       <c r="I7" s="0">
-        <v>0.47092729806900024</v>
+        <v>0.59360659122467041</v>
       </c>
       <c r="J7" s="0">
-        <v>0.47087478637695312</v>
+        <v>0.58538967370986939</v>
       </c>
       <c r="K7" s="0">
-        <v>0.48044899106025696</v>
+        <v>0.5881994366645813</v>
       </c>
       <c r="L7" s="0">
-        <v>0.44739821553230286</v>
+        <v>0.56963133811950684</v>
       </c>
       <c r="M7" s="0">
-        <v>0.46200442314147949</v>
+        <v>0.57682937383651733</v>
       </c>
       <c r="N7" s="0">
-        <v>0.40859237313270569</v>
+        <v>0.5171617865562439</v>
       </c>
       <c r="O7" s="0">
-        <v>0.47217199206352234</v>
+        <v>0.59737128019332886</v>
       </c>
     </row>
     <row r="8">
@@ -553,40 +554,40 @@
         <v>29</v>
       </c>
       <c r="D8" s="0">
-        <v>0.48026904463768005</v>
+        <v>0.53313297033309937</v>
       </c>
       <c r="E8" s="0">
-        <v>0.44006219506263733</v>
+        <v>0.47876071929931641</v>
       </c>
       <c r="F8" s="0">
-        <v>0.46740254759788513</v>
+        <v>0.49027886986732483</v>
       </c>
       <c r="G8" s="0">
-        <v>0.44739857316017151</v>
+        <v>0.47752785682678223</v>
       </c>
       <c r="H8" s="0">
-        <v>0.48086622357368469</v>
+        <v>0.50337439775466919</v>
       </c>
       <c r="I8" s="0">
-        <v>0.48486897349357605</v>
+        <v>0.52837085723876953</v>
       </c>
       <c r="J8" s="0">
-        <v>0.45814222097396851</v>
+        <v>0.51589924097061157</v>
       </c>
       <c r="K8" s="0">
-        <v>0.46512141823768616</v>
+        <v>0.51963919401168823</v>
       </c>
       <c r="L8" s="0">
-        <v>0.44971010088920593</v>
+        <v>0.47904351353645325</v>
       </c>
       <c r="M8" s="0">
-        <v>0.45741447806358337</v>
+        <v>0.50672811269760132</v>
       </c>
       <c r="N8" s="0">
-        <v>0.42156270146369934</v>
+        <v>0.44872066378593445</v>
       </c>
       <c r="O8" s="0">
-        <v>0.49802449345588684</v>
+        <v>0.49527806043624878</v>
       </c>
     </row>
     <row r="9">
@@ -600,40 +601,40 @@
         <v>30</v>
       </c>
       <c r="D9" s="0">
-        <v>0.51858490705490112</v>
+        <v>0.4701877236366272</v>
       </c>
       <c r="E9" s="0">
-        <v>0.5189012885093689</v>
+        <v>0.43046632409095764</v>
       </c>
       <c r="F9" s="0">
-        <v>0.49528679251670837</v>
+        <v>0.42905673384666443</v>
       </c>
       <c r="G9" s="0">
-        <v>0.48932719230651855</v>
+        <v>0.41725245118141174</v>
       </c>
       <c r="H9" s="0">
-        <v>0.50279468297958374</v>
+        <v>0.47804164886474609</v>
       </c>
       <c r="I9" s="0">
-        <v>0.5211675763130188</v>
+        <v>0.45900750160217285</v>
       </c>
       <c r="J9" s="0">
-        <v>0.50174903869628906</v>
+        <v>0.44932708144187927</v>
       </c>
       <c r="K9" s="0">
-        <v>0.50588232278823853</v>
+        <v>0.48374888300895691</v>
       </c>
       <c r="L9" s="0">
-        <v>0.47697007656097412</v>
+        <v>0.42898997664451599</v>
       </c>
       <c r="M9" s="0">
-        <v>0.51346403360366821</v>
+        <v>0.45138362050056458</v>
       </c>
       <c r="N9" s="0">
-        <v>0.45386689901351929</v>
+        <v>0.39386698603630066</v>
       </c>
       <c r="O9" s="0">
-        <v>0.49753275513648987</v>
+        <v>0.44646719098091125</v>
       </c>
     </row>
     <row r="10">
@@ -647,40 +648,40 @@
         <v>31</v>
       </c>
       <c r="D10" s="0">
-        <v>0.5509067177772522</v>
+        <v>0.41294094920158386</v>
       </c>
       <c r="E10" s="0">
-        <v>0.49874365329742432</v>
+        <v>0.38774234056472778</v>
       </c>
       <c r="F10" s="0">
-        <v>0.51566904783248901</v>
+        <v>0.37651106715202332</v>
       </c>
       <c r="G10" s="0">
-        <v>0.49974915385246277</v>
+        <v>0.34752175211906433</v>
       </c>
       <c r="H10" s="0">
-        <v>0.52645516395568848</v>
+        <v>0.3905588686466217</v>
       </c>
       <c r="I10" s="0">
-        <v>0.54575300216674805</v>
+        <v>0.39055371284484863</v>
       </c>
       <c r="J10" s="0">
-        <v>0.53456217050552368</v>
+        <v>0.36934199929237366</v>
       </c>
       <c r="K10" s="0">
-        <v>0.53121805191040039</v>
+        <v>0.39750245213508606</v>
       </c>
       <c r="L10" s="0">
-        <v>0.50906717777252197</v>
+        <v>0.38523215055465698</v>
       </c>
       <c r="M10" s="0">
-        <v>0.53802239894866943</v>
+        <v>0.39111322164535522</v>
       </c>
       <c r="N10" s="0">
-        <v>0.48076099157333374</v>
+        <v>0.34462469816207886</v>
       </c>
       <c r="O10" s="0">
-        <v>0.53861534595489502</v>
+        <v>0.40056878328323364</v>
       </c>
     </row>
     <row r="11">
@@ -694,40 +695,40 @@
         <v>32</v>
       </c>
       <c r="D11" s="0">
-        <v>0.44492840766906738</v>
+        <v>0.41317188739776611</v>
       </c>
       <c r="E11" s="0">
-        <v>0.41336488723754883</v>
+        <v>0.40324723720550537</v>
       </c>
       <c r="F11" s="0">
-        <v>0.43742677569389343</v>
+        <v>0.39805182814598084</v>
       </c>
       <c r="G11" s="0">
-        <v>0.42294800281524658</v>
+        <v>0.37392988801002502</v>
       </c>
       <c r="H11" s="0">
-        <v>0.43272578716278076</v>
+        <v>0.42720839381217957</v>
       </c>
       <c r="I11" s="0">
-        <v>0.43691787123680115</v>
+        <v>0.42000865936279297</v>
       </c>
       <c r="J11" s="0">
-        <v>0.43084549903869629</v>
+        <v>0.38936766982078552</v>
       </c>
       <c r="K11" s="0">
-        <v>0.43634992837905884</v>
+        <v>0.41757997870445252</v>
       </c>
       <c r="L11" s="0">
-        <v>0.41298156976699829</v>
+        <v>0.40414223074913025</v>
       </c>
       <c r="M11" s="0">
-        <v>0.43350079655647278</v>
+        <v>0.40940168499946594</v>
       </c>
       <c r="N11" s="0">
-        <v>0.36684346199035645</v>
+        <v>0.35451671481132507</v>
       </c>
       <c r="O11" s="0">
-        <v>0.43666067719459534</v>
+        <v>0.42726603150367737</v>
       </c>
     </row>
   </sheetData>

--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/group_roi_means_wmprob.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/group_roi_means_wmprob.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
